--- a/backtest_runs/20260410_193731/by_symbol/MRNS/MRNS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/MRNS/MRNS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-2854.499999999998</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>97145.5</v>
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="I6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>97145.5</v>
@@ -817,7 +817,7 @@
         <v>-3079.400000000002</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>96142.10000000001</v>
@@ -863,7 +863,7 @@
         <v>-1712.700000000003</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>94429.39999999999</v>
@@ -909,7 +909,7 @@
         <v>-2006.799999999994</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>92422.60000000001</v>
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="I12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>96332.40000000001</v>
@@ -1139,7 +1139,7 @@
         <v>-501.6999999999985</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>97560.70000000001</v>
@@ -1185,7 +1185,7 @@
         <v>-138.4000000000094</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>97422.3</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>97422.3</v>
@@ -1415,7 +1415,7 @@
         <v>-1297.5</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100501.7</v>
@@ -1461,7 +1461,7 @@
         <v>-2231.699999999998</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>98270</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>100674.7</v>
@@ -1645,7 +1645,7 @@
         <v>-622.799999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>100051.9</v>
